--- a/data/trans_orig/IP3111_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29954</t>
+          <t>29396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34350</t>
+          <t>34694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56302</t>
+          <t>55616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20798</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37720</t>
+          <t>37276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27883</t>
+          <t>28644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50939</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54432</t>
+          <t>52663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80283</t>
+          <t>80695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>18281</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>32454</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35327</t>
+          <t>34314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52196</t>
+          <t>51109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31160</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>15494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29668</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40591</t>
+          <t>38384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>28597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21996</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46300</t>
+          <t>45802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29259</t>
+          <t>29665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>27568</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45501</t>
+          <t>44923</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>28918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>30386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34281</t>
+          <t>33998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53631</t>
+          <t>53941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22066</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22471</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40176</t>
+          <t>40837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>18348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>34260</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11085</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25278</t>
+          <t>25976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35482</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20347</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>34959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14235</t>
+          <t>14297</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23312</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>21403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21597</t>
+          <t>21259</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>36278</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27112</t>
+          <t>27362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33347</t>
+          <t>32882</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>57045</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19453</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>43176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>34339</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58400</t>
+          <t>58293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59717</t>
+          <t>57438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96218</t>
+          <t>95658</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>29334</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>62802</t>
+          <t>62438</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41116</t>
+          <t>41826</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>66046</t>
+          <t>64743</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>78479</t>
+          <t>78482</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>121815</t>
+          <t>120389</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53168</t>
+          <t>55533</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50756</t>
+          <t>51580</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61143</t>
+          <t>61866</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>96842</t>
+          <t>98480</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118880</t>
+          <t>104137</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19495</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>45339</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49237</t>
+          <t>48775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>148127</t>
+          <t>157628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>31568</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44056</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>37740</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>67737</t>
+          <t>68124</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28630</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>39812</t>
+          <t>40015</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>22308</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>42145</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>32249</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55865</t>
+          <t>55627</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21338</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>41309</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>49449</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>75608</t>
+          <t>76489</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>19395</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>37423</t>
+          <t>36970</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>32985</t>
+          <t>34771</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>39594</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>66463</t>
+          <t>64654</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21830</t>
+          <t>21097</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>22617</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>42791</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>26647</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>21803</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>62357</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39852</t>
+          <t>39423</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>84260</t>
+          <t>83008</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>808</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>17536</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>29777</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14854</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>24486</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>18115</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>35109</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>16498</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>31986</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>17462</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>18325</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>35132</t>
+          <t>35517</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>40243</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>75773</t>
+          <t>75618</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>109728</t>
+          <t>109473</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>70686</t>
+          <t>71196</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>102224</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>157624</t>
+          <t>155195</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>202793</t>
+          <t>200791</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>91793</t>
+          <t>91269</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>128988</t>
+          <t>127446</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>137407</t>
+          <t>138758</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>181998</t>
+          <t>183849</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>240620</t>
+          <t>237444</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>300776</t>
+          <t>299371</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>115606</t>
+          <t>116102</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>159616</t>
+          <t>158539</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>142045</t>
+          <t>141240</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>184472</t>
+          <t>183480</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,47 +5776,47 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>300385</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>267190</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>328265</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>21,92%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
           <t>19,5%</t>
         </is>
       </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>25,33%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>300385</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>268374</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>333164</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>21,92%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>99814</t>
+          <t>98619</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>138782</t>
+          <t>140579</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>105116</t>
+          <t>103944</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>145120</t>
+          <t>143848</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>217456</t>
+          <t>214355</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>271284</t>
+          <t>269662</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>79446</t>
+          <t>77395</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>195367</t>
+          <t>177300</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>74155</t>
+          <t>74908</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>112435</t>
+          <t>113714</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>165946</t>
+          <t>165852</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>285772</t>
+          <t>282310</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>62939</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>94942</t>
+          <t>95325</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>82253</t>
+          <t>83716</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>141341</t>
+          <t>139792</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,47 +6115,47 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>19,19%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>182138</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>154748</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>223985</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13,29%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
           <t>11,29%</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>182138</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>154213</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>221754</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>13,29%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3111_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20746</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14317</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28369</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22024</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15320</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29396</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>30764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44466</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>33396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55616</t>
+          <t>54866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33339</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24892</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43095</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>35,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>27827</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20366</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37276</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>27,36%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38179</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50194</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>66006</t>
+          <t>58698</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52663</t>
+          <t>48104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80695</t>
+          <t>71300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17574</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33550</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,68%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16315</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11155</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23882</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26232</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35239</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>53454</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23289</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15876</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32058</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16167</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10793</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23247</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,9%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34314</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>49201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13625</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8485</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22043</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9928</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5708</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15655</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>23633</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33514</t>
+          <t>32157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4968</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9449</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4997</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15494</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>14864</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11767</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38384</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>319</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13403</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8197</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20433</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21086</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14966</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28597</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>30,62%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>21823</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>28966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>35227</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45802</t>
+          <t>45695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20892</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14910</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28145</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,24%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13644</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8664</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19849</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29665</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35886</t>
+          <t>35151</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27568</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44923</t>
+          <t>44113</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21006</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14182</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28415</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>21431</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14941</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28918</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>21591</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43431</t>
+          <t>42596</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33998</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53941</t>
+          <t>52765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9455</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22085</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>15309</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>10516</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22657</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>30143</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40837</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12796</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8213</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>19958</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12177</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>7472</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>18348</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>18265</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>35068</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3518</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11969</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9745</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5447</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15074</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>95410</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>93708</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>265</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6965</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12502</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8207</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4342</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13735</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>16,38%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>14948</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25976</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10783</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5908</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17348</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>31,06%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7245</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17943</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>24,2%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>35,82%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25081</t>
+          <t>23426</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12885</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8636</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19081</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>15,47%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>34,17%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>12794</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7812</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18620</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>37,17%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13849</t>
+          <t>13197</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19279</t>
+          <t>18903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34959</t>
+          <t>34806</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>7584</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>12380</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>7733</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>12801</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>16150</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>22448</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9136</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5036</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14864</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>16,36%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5447</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2432</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8491</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4337</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14496</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>25,96%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>3788</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7607</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>19751</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>151</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>15766</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9967</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>22858</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>25979</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>16654</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>36278</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>17911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27362</t>
+          <t>32625</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>44296</t>
+          <t>41216</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32882</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57045</t>
+          <t>52549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>42334</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>32368</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>56428</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>31447</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>19578</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>43176</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14,59%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>28435</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34339</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58293</t>
+          <t>36982</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>76245</t>
+          <t>70769</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>57438</t>
+          <t>57265</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95658</t>
+          <t>86155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>48557</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>38040</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>60076</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>30,45%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>46404</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>29334</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>62438</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>21,53%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>13,61%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>28,97%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53086</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>32671</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>64743</t>
+          <t>50734</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>99490</t>
+          <t>89853</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>78482</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>120389</t>
+          <t>106434</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>36827</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>27716</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>48380</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>18,66%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>24,52%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>41001</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>27145</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>55533</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>19,02%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>25,76%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29137</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51580</t>
+          <t>47290</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>80094</t>
+          <t>74801</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61866</t>
+          <t>62877</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>98480</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>24994</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>16707</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>37446</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>49641</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>23605</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>104137</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>48,32%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>28124</t>
+          <t>25835</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>18729</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>37639</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>77766</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48775</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>157628</t>
+          <t>67345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>28835</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>19905</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>41316</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>20,94%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>21064</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>12546</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>31568</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>29240</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>50305</t>
+          <t>46485</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>35504</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68124</t>
+          <t>61723</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>176640</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>176640</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>176640</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>212658</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>544</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>17590</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>11757</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>25656</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>17,94%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>10699</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>6882</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>17217</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12729</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>30061</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>40015</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>29282</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>21330</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>39858</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>20,48%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>11429</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>7350</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>18169</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>12057</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>7362</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>18915</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>10,53%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>31764</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>22308</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>43266</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>41339</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>31293</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>53191</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>27537</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>19628</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>37348</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>13,73%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>26,12%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>31620</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>23842</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>40235</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>20,84%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>30795</t>
+          <t>33105</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>25493</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>41398</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>62416</t>
+          <t>60642</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>49341</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>76489</t>
+          <t>72378</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>15350</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>31638</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>15,92%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>10,74%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>27265</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>19395</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>36970</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>32,32%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>25221</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>34771</t>
+          <t>34134</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>47979</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>64654</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>14136</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>8718</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>21725</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>9,89%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>14367</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>9277</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>21097</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>9635</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>21815</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>42317</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>31671</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>21177</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>51919</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>36,31%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>19006</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>12817</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>26538</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>34496</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>21803</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>62357</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>50452</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>83008</t>
+          <t>75625</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>142974</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>142974</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>142974</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>114387</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>114387</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>114387</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>114501</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>114501</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>114501</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>156940</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>156940</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>156940</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>361</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>257475</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>257475</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>257475</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4695,72 +4695,72 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>2497</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>4867</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>2235</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>9703</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -4808,72 +4808,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>9923</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>5723</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>15313</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>23,79%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>12304</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>7881</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>17536</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>18,37%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>26,18%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>29777</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -4921,72 +4921,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>15149</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>9748</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>21362</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>23,54%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>33,19%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>9143</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>5469</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>14621</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>21,83%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24486</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>25859</t>
+          <t>24443</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>35109</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -5034,72 +5034,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11497</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>6940</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>18714</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11187</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>6918</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>16747</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>11370</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18952</t>
+          <t>17805</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>22867</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>31754</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -5147,72 +5147,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>6526</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>18115</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>17,74%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>10,14%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>28,15%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>14304</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>9441</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>20876</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>21,36%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>24835</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>34396</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -5260,72 +5260,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13873</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>8727</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>21272</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>21,56%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>33,05%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>15169</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>9470</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>22524</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>22,65%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>33,63%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>30438</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>40243</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -5373,74 +5373,74 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>64358</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>64358</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>64358</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>66975</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>66975</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>66975</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>68348</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>68348</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>68348</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>67570</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>67570</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>67570</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>180</t>
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>134545</t>
+          <t>132706</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>134545</t>
+          <t>132706</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>134545</t>
+          <t>132706</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5490,72 +5490,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>76967</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>63764</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>92235</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>13,73%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>92862</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>75618</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>109473</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>86540</t>
+          <t>92948</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>71196</t>
+          <t>78238</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>103181</t>
+          <t>109661</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>179402</t>
+          <t>169915</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>155195</t>
+          <t>151156</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>200791</t>
+          <t>192247</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -5603,72 +5603,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>146553</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>127756</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>168691</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>21,82%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>19,02%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>25,12%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>108773</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>91269</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>127446</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>19,85%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>160062</t>
+          <t>105680</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>138758</t>
+          <t>92193</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>183849</t>
+          <t>122404</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>268834</t>
+          <t>252232</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>237444</t>
+          <t>227798</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>299371</t>
+          <t>278383</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -5716,72 +5716,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>150375</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>131921</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>173142</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>137706</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>116102</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>158539</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>21,45%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>24,69%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>162679</t>
+          <t>135279</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>141240</t>
+          <t>118232</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>183480</t>
+          <t>153771</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>300385</t>
+          <t>285655</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>267190</t>
+          <t>259119</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>328265</t>
+          <t>312004</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -5829,72 +5829,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>116940</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>98639</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>135370</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20,16%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>118663</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>98619</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>140579</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>123317</t>
+          <t>113813</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>103944</t>
+          <t>97182</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>143848</t>
+          <t>129689</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>241980</t>
+          <t>230752</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>214355</t>
+          <t>206897</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>269662</t>
+          <t>256376</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -5942,72 +5942,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>86107</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>71674</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>103499</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>105864</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>77395</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>177300</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>27,61%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>91873</t>
+          <t>82487</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>74908</t>
+          <t>68682</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>113714</t>
+          <t>98392</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>197737</t>
+          <t>168594</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>165852</t>
+          <t>147786</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>282310</t>
+          <t>191806</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -6055,72 +6055,72 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>94636</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>75735</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>127766</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>14,09%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>19,02%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>78222</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63551</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>95325</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>14,85%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>103917</t>
+          <t>77052</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>83716</t>
+          <t>63165</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>139792</t>
+          <t>92269</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>182138</t>
+          <t>171688</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>154748</t>
+          <t>147448</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>223985</t>
+          <t>207129</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -6168,74 +6168,74 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>671578</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>671578</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>671578</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>642089</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>642089</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>642089</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>607258</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>607258</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>607258</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>921</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>728387</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>728387</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>728387</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>1820</t>
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1370476</t>
+          <t>1278836</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1370476</t>
+          <t>1278836</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1370476</t>
+          <t>1278836</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
